--- a/Pruebas/Usabilidad/Registro Pruebas de Usabilidad.xlsx
+++ b/Pruebas/Usabilidad/Registro Pruebas de Usabilidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yagon\Desktop\Clase\Quinto año\TFG\Aplicacion\Pruebas\Usabilidad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B5BF94-32C0-4260-BA62-A84D2B8518C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9A876C-8AA6-40D2-B3BC-167AC14F32BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preguntas" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>¿Cuál es la formación táctica con peor media de ataque?</t>
   </si>
@@ -103,9 +103,6 @@
     <t>Tiempo total</t>
   </si>
   <si>
-    <t>Problemas  de usabildad</t>
-  </si>
-  <si>
     <t>Ayudas solicitadas</t>
   </si>
   <si>
@@ -128,6 +125,12 @@
   </si>
   <si>
     <t>Satisfacción general</t>
+  </si>
+  <si>
+    <t>Edad</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -220,12 +223,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -249,6 +263,12 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -548,15 +568,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M8"/>
+  <dimension ref="B2:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="9" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" customWidth="1"/>
-    <col min="13" max="13" width="105.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="105.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C2" s="3"/>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -576,12 +596,12 @@
       <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
@@ -606,14 +626,14 @@
       <c r="I3" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="K3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
@@ -638,14 +658,14 @@
       <c r="I4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
@@ -653,31 +673,31 @@
         <v>15</v>
       </c>
       <c r="D5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
@@ -685,43 +705,43 @@
         <v>16</v>
       </c>
       <c r="D6" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="8" t="b">
         <v>0</v>
       </c>
       <c r="G6" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L7" s="4" t="s">
+    <row r="7" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L8" s="4" t="s">
+    <row r="8" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -733,7 +753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62363DCF-42E4-4282-A412-73A31521266E}">
-  <dimension ref="B2:H6"/>
+  <dimension ref="B2:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="31.44140625" customWidth="1"/>
@@ -744,22 +764,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
@@ -815,11 +834,21 @@
       <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7">
+        <v>5</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
@@ -828,11 +857,46 @@
       <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="D6" s="7">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7">
+        <v>4</v>
+      </c>
+      <c r="F6" s="7">
+        <v>4</v>
+      </c>
+      <c r="G6" s="7">
+        <v>4</v>
+      </c>
+      <c r="H6" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="7">
+        <f>SUM(D3:D6 ) /4</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" ref="E7:H7" si="0">SUM(E3:E6 ) /4</f>
+        <v>3.75</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -841,15 +905,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA069438-7099-4D26-9753-785A79E216B5}">
-  <dimension ref="B2:I6"/>
+  <dimension ref="B2:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="15.109375" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" customWidth="1"/>
-    <col min="9" max="9" width="29.21875" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
@@ -862,16 +925,16 @@
         <v>20</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
@@ -885,18 +948,20 @@
         <f>COUNTIF(Preguntas!D3:I3,"VERDADERO") / 6</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="10">
+        <v>0.34166666666666667</v>
+      </c>
       <c r="F3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H3" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I3" s="7">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -910,18 +975,20 @@
         <f>COUNTIF(Preguntas!D4:I4,"VERDADERO") / 6</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="10">
+        <v>0.30833333333333335</v>
+      </c>
       <c r="F4" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I4" s="7">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -933,16 +1000,22 @@
       </c>
       <c r="D5" s="9">
         <f>COUNTIF(Preguntas!D5:I5,"VERDADERO") / 6</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.28958333333333336</v>
+      </c>
+      <c r="F5" s="7">
         <v>0</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="G5" s="7">
+        <v>8</v>
+      </c>
       <c r="H5" s="7">
         <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -954,16 +1027,51 @@
       </c>
       <c r="D6" s="9">
         <f>COUNTIF(Preguntas!D6:I6,"VERDADERO") / 6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3</v>
+      </c>
+      <c r="G6" s="7">
+        <v>3</v>
+      </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="7">
-        <v>2</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="9">
+        <f>SUM(D3:D6 ) /4</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" ref="E7:I7" si="0">SUM(E3:E6 ) /4</f>
+        <v>0.34045138888888893</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>32.25</v>
       </c>
     </row>
   </sheetData>

--- a/Pruebas/Usabilidad/Registro Pruebas de Usabilidad.xlsx
+++ b/Pruebas/Usabilidad/Registro Pruebas de Usabilidad.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9A876C-8AA6-40D2-B3BC-167AC14F32BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preguntas" sheetId="1" r:id="rId1"/>
